--- a/docs/hoja_editable.xlsx
+++ b/docs/hoja_editable.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="hoja" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="53">
   <si>
     <t xml:space="preserve">FORM-</t>
   </si>
@@ -90,10 +90,19 @@
     <t xml:space="preserve">EMPRESA ESTATAL DE PRODUCCIÓN Y COMERCIALIZACIÓN DEL ORO - EPCORO</t>
   </si>
   <si>
+    <t xml:space="preserve">Caja de Salud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hacer un if</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nº NIM</t>
   </si>
   <si>
     <t xml:space="preserve">02-2388-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor Neto</t>
   </si>
   <si>
     <t xml:space="preserve">Nº NIT</t>
@@ -1178,23 +1187,29 @@
         <v>19</v>
       </c>
       <c r="D11" s="14"/>
-      <c r="E11" s="13"/>
+      <c r="E11" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="F11" s="21"/>
       <c r="G11" s="13"/>
-      <c r="H11" s="22"/>
+      <c r="H11" s="22" t="s">
+        <v>21</v>
+      </c>
       <c r="I11" s="23"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
       <c r="B12" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" s="14"/>
-      <c r="E12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
@@ -1204,7 +1219,7 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7"/>
       <c r="B13" s="9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>1006965023</v>
@@ -1280,7 +1295,7 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C19" s="32"/>
       <c r="D19" s="14"/>
@@ -1294,10 +1309,10 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
       <c r="B20" s="13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="9"/>
@@ -1310,7 +1325,7 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
       <c r="B21" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C21" s="29" t="str">
         <f aca="false">[1]NOMBRES!F3</f>
@@ -1327,7 +1342,7 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C22" s="38" t="n">
         <f aca="false">[1]NOMBRES!G3</f>
@@ -1380,7 +1395,7 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="14"/>
@@ -1394,7 +1409,7 @@
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C27" s="41" t="str">
         <f aca="false">[1]NOMBRES!H3</f>
@@ -1411,7 +1426,7 @@
     <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C28" s="42" t="str">
         <f aca="false">[1]NOMBRES!I3</f>
@@ -1428,7 +1443,7 @@
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="43" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C29" s="39" t="n">
         <f aca="false">[1]NOMBRES!J3</f>
@@ -1445,7 +1460,7 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C30" s="39" t="str">
         <f aca="false">[1]NOMBRES!K3</f>
@@ -1462,7 +1477,7 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C31" s="39" t="str">
         <f aca="false">[1]NOMBRES!L3</f>
@@ -1479,7 +1494,7 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C32" s="39" t="str">
         <f aca="false">[1]NOMBRES!M3</f>
@@ -1496,7 +1511,7 @@
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
       <c r="B33" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C33" s="39" t="n">
         <f aca="false">[1]NOMBRES!N3</f>
@@ -1513,7 +1528,7 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C34" s="39" t="str">
         <f aca="false">[1]NOMBRES!O3</f>
@@ -1542,7 +1557,7 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="14"/>
@@ -1556,10 +1571,10 @@
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
       <c r="B37" s="9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="9"/>
@@ -1572,7 +1587,7 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7"/>
       <c r="B38" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C38" s="46" t="n">
         <f aca="false">[1]NOMBRES!P3</f>
@@ -1589,7 +1604,7 @@
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C39" s="47" t="n">
         <f aca="false">[1]NOMBRES!Q3</f>
@@ -1606,7 +1621,7 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
       <c r="B40" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C40" s="48" t="n">
         <f aca="false">C39*C38</f>
@@ -1809,7 +1824,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="13" t="s">
@@ -1878,10 +1893,10 @@
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
       <c r="B12" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="9"/>
@@ -1894,7 +1909,7 @@
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7"/>
       <c r="B13" s="9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>1006965023</v>
@@ -1970,7 +1985,7 @@
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C19" s="32"/>
       <c r="D19" s="14"/>
@@ -1984,10 +1999,10 @@
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
       <c r="B20" s="13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="9"/>
@@ -2000,10 +2015,10 @@
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
       <c r="B21" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="9"/>
@@ -2016,7 +2031,7 @@
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C22" s="38" t="n">
         <v>5956713</v>
@@ -2068,7 +2083,7 @@
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="14"/>
@@ -2082,10 +2097,10 @@
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="9"/>
@@ -2098,10 +2113,10 @@
     <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="13"/>
@@ -2114,7 +2129,7 @@
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="43" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C29" s="39" t="n">
         <v>1500735</v>
@@ -2130,10 +2145,10 @@
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="9"/>
@@ -2146,10 +2161,10 @@
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="9"/>
@@ -2162,10 +2177,10 @@
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="9"/>
@@ -2178,7 +2193,7 @@
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
       <c r="B33" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C33" s="39" t="n">
         <v>20633</v>
@@ -2194,10 +2209,10 @@
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="9"/>
@@ -2222,7 +2237,7 @@
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="14"/>
@@ -2236,10 +2251,10 @@
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
       <c r="B37" s="9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="9"/>
@@ -2252,7 +2267,7 @@
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7"/>
       <c r="B38" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C38" s="46" t="n">
         <v>1944.53</v>
@@ -2268,7 +2283,7 @@
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C39" s="47" t="n">
         <v>0.9302</v>
@@ -2284,7 +2299,7 @@
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
       <c r="B40" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C40" s="50" t="n">
         <v>1808.801806</v>
